--- a/experiments/results/mobilenetv2_imagenet/ImageNet-1K/DICE/adaptive/max/results.xlsx
+++ b/experiments/results/mobilenetv2_imagenet/ImageNet-1K/DICE/adaptive/max/results.xlsx
@@ -342,7 +342,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="11" max="11"/>
@@ -725,6 +725,117 @@
       <c r="K10" s="4" t="inlineStr">
         <is>
           <t>dice_p=50,ash_p=None,react_th=None,scale_th=1.0,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>35.41</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>91.63</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>50.59</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>87.28</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>95.87</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>33.37</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>93.63</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>33.77</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=10,ash_p=None,react_th=None,scale_th=1.0,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>37.81</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>51.92</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>19.43</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>94.81</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>37.28</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>92.87</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>36.61</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>91.31999999999999</v>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=10,ash_p=None,react_th=None,scale_th=0.1,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>50.45</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>87.31999999999999</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>96.22</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>32.41</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>93.84999999999999</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>33.15</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=10,ash_p=None,react_th=None,scale_th=1.5,type=max</t>
         </is>
       </c>
     </row>
